--- a/slide_classification/TCGA_Results/Averaging/H-Optimus-1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Averaging/H-Optimus-1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -578,26 +579,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[[85  3]
- [ 8  7]]</t>
+          <t>[[85, 3], [8, 7]]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[[83  1]
- [ 4  9]]</t>
+          <t>[[83, 1], [4, 9]]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[[88  4]
- [ 6 14]]</t>
+          <t>[[88, 4], [6, 14]]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[[83  6]
- [ 9  3]]</t>
+          <t>[[83, 6], [9, 3]]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -613,19 +610,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8640776699029126</v>
+        <v>0.8543689320388349</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8969072164948454</v>
+        <v>0.8144329896907216</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8660714285714286</v>
+        <v>0.7946428571428571</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8217821782178217</v>
+        <v>0.801980198019802</v>
       </c>
       <c r="F8" t="n">
-        <v>0.862209623296752</v>
+        <v>0.8163562442230539</v>
       </c>
     </row>
     <row r="9">
@@ -635,19 +632,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8098484848484848</v>
+        <v>0.8041666666666667</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8104395604395604</v>
+        <v>0.7628205128205128</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8597826086956522</v>
+        <v>0.7967391304347826</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7546816479400749</v>
+        <v>0.7434456928838951</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8086880754809431</v>
+        <v>0.7767930007014643</v>
       </c>
     </row>
     <row r="10">
@@ -657,19 +654,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7643790849673202</v>
+        <v>0.7529185990724452</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7913080895008606</v>
+        <v>0.6930379746835442</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8040816326530612</v>
+        <v>0.7228617536309844</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6817226890756303</v>
+        <v>0.6619812583668006</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7603728740492182</v>
+        <v>0.7076998964384436</v>
       </c>
     </row>
     <row r="11">
@@ -679,19 +676,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8730059013896821</v>
+        <v>0.8651288158383005</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8999680607555406</v>
+        <v>0.8343338118230458</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8749271137026239</v>
+        <v>0.8135326212249289</v>
       </c>
       <c r="E11" t="n">
-        <v>0.842686579582328</v>
+        <v>0.8278261561095868</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8726469138575437</v>
+        <v>0.8352053512489654</v>
       </c>
     </row>
     <row r="12">
@@ -701,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9204545454545454</v>
+        <v>0.8977272727272727</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8736263736263736</v>
+        <v>0.8910256410256411</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9097826086956522</v>
+        <v>0.9092391304347827</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8614232209737828</v>
+        <v>0.8146067415730337</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8913216871875884</v>
+        <v>0.8781496964401825</v>
       </c>
     </row>
     <row r="13">
@@ -724,31 +721,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[78 10]
- [ 4 11]]</t>
+          <t>[[77, 11], [4, 11]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[78  6]
- [ 4  9]]</t>
+          <t>[[70, 14], [4, 9]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[80 12]
- [ 3 17]]</t>
+          <t>[[73, 19], [4, 16]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[75 14]
- [ 4  8]]</t>
+          <t>[[73, 16], [4, 8]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[78, 10], [4, 11]]</t>
+          <t>[[73, 15], [4, 11]]</t>
         </is>
       </c>
     </row>
@@ -870,26 +863,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[[86  2]
- [11  4]]</t>
+          <t>[[86, 2], [11, 4]]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[[84  0]
- [11  2]]</t>
+          <t>[[84, 0], [11, 2]]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[[89  3]
- [12  8]]</t>
+          <t>[[89, 3], [12, 8]]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[[86  3]
- [ 8  4]]</t>
+          <t>[[86, 3], [8, 4]]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1016,26 +1005,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[[74 14]
- [ 4 11]]</t>
+          <t>[[74, 14], [4, 11]]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[[63 21]
- [ 7  6]]</t>
+          <t>[[63, 21], [7, 6]]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[[81 11]
- [ 4 16]]</t>
+          <t>[[81, 11], [4, 16]]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[[77 12]
- [ 5  7]]</t>
+          <t>[[77, 12], [5, 7]]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1054,16 +1039,16 @@
         <v>0.9320388349514563</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9175257731958762</v>
+        <v>0.9072164948453608</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8482142857142857</v>
+        <v>0.8660714285714286</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8811881188118812</v>
+        <v>0.900990099009901</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8947417531683748</v>
+        <v>0.9015792143445367</v>
       </c>
     </row>
     <row r="27">
@@ -1073,19 +1058,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7943181818181818</v>
+        <v>0.821969696969697</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6532608695652173</v>
+        <v>0.683695652173913</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6441947565543071</v>
+        <v>0.6554307116104868</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6960203750613496</v>
+        <v>0.7037355536500627</v>
       </c>
     </row>
     <row r="28">
@@ -1095,19 +1080,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8406629834254143</v>
+        <v>0.850817297744672</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7550505050505051</v>
+        <v>0.7098703888334995</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6817650008357011</v>
+        <v>0.7192044125020892</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6670329670329671</v>
+        <v>0.6950483091787439</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7361278640861468</v>
+        <v>0.7437351020647511</v>
       </c>
     </row>
     <row r="29">
@@ -1117,19 +1102,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9261814085715817</v>
+        <v>0.9288327216406622</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9010725814849527</v>
+        <v>0.8850150579190263</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8297199207277763</v>
+        <v>0.8497528712303908</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8706125557610706</v>
+        <v>0.8861027407088535</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8818966166363453</v>
+        <v>0.8874258478747332</v>
       </c>
     </row>
     <row r="30">
@@ -1139,19 +1124,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9340909090909091</v>
+        <v>0.9037878787878788</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8855311355311355</v>
+        <v>0.9258241758241759</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8983695652173913</v>
+        <v>0.8940217391304348</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8595505617977528</v>
+        <v>0.8726591760299626</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8943855429092972</v>
+        <v>0.899073242443113</v>
       </c>
     </row>
     <row r="31">
@@ -1162,31 +1147,413 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[[87  1]
- [ 6  9]]</t>
+          <t>[[86, 2], [5, 10]]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[[84  0]
- [ 8  5]]</t>
+          <t>[[84, 0], [9, 4]]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[[88  4]
- [13  7]]</t>
+          <t>[[89, 3], [12, 8]]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[[85  4]
- [ 8  4]]</t>
+          <t>[[87, 2], [8, 4]]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[[86, 2], [9, 6]]</t>
+          <t>[[86, 2], [8, 6]]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Classifier</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>N_folds</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>N_test</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>acc_sd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>bacc</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>bacc_sd</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_sd</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_f1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_f1_sd</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>auroc</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>auroc_sd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>conf_matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>H-Optimus-1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>413</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9009642314929264</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.03485221339903614</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7440105870965055</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1005513169292886</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.767314433855969</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1064251012971155</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8951239569948941</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.03763283527669362</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.9096312817413819</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.02893830501861727</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>[[85, 4], [7, 8]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>H-Optimus-1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ann</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>413</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8163562442230539</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.02305864927694515</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7767930007014643</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.02477114771248951</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7076998964384436</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.03383703148217181</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.8352053512489654</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.01884365318615214</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8781496964401825</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.03726033904031788</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>[[73, 15], [4, 11]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H-Optimus-1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>knn</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>413</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.87938622084841</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.009970055858484891</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.633100290037271</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.03911190941073106</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6644060537934922</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.04231504455496705</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8565779387045503</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.01252132578099531</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.7643647281516724</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0361095129175061</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>[[86, 2], [10, 4]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H-Optimus-1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>proto</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>413</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8085843803801073</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.05824998788800899</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7393396926310948</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.08736149401068243</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.6885063853634283</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.08652237438462519</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.8277991258618528</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.04718313043986419</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.8308655519696067</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.1233760839929797</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>[[74, 14], [5, 10]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H-Optimus-1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>413</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9015792143445367</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.02356224377234104</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.7037355536500627</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.06928784214233448</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.7437351020647511</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.06242109812758106</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.8874258478747332</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.02802385093583539</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.899073242443113</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0191119126647346</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>[[86, 2], [8, 6]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/TCGA_Results/Averaging/H-Optimus-1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Averaging/H-Optimus-1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -849,10 +849,10 @@
         <v>0.7494565217391305</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8000936329588014</v>
+        <v>0.7598314606741572</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7643647281516724</v>
+        <v>0.7542991850805114</v>
       </c>
     </row>
     <row r="19">
@@ -1430,10 +1430,10 @@
         <v>0.01252132578099531</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7643647281516724</v>
+        <v>0.7542991850805114</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0361095129175061</v>
+        <v>0.02980907134830932</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>

--- a/slide_classification/TCGA_Results/Averaging/H-Optimus-1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Averaging/H-Optimus-1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -610,19 +610,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8543689320388349</v>
+        <v>0.8349514563106796</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8144329896907216</v>
+        <v>0.8247422680412371</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7946428571428571</v>
+        <v>0.8035714285714286</v>
       </c>
       <c r="E8" t="n">
-        <v>0.801980198019802</v>
+        <v>0.8217821782178217</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8163562442230539</v>
+        <v>0.8212618327852916</v>
       </c>
     </row>
     <row r="9">
@@ -632,19 +632,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8041666666666667</v>
+        <v>0.8204545454545455</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7628205128205128</v>
+        <v>0.7687728937728937</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7967391304347826</v>
+        <v>0.8217391304347825</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7434456928838951</v>
+        <v>0.7907303370786517</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7767930007014643</v>
+        <v>0.8004242266852183</v>
       </c>
     </row>
     <row r="10">
@@ -654,19 +654,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7529185990724452</v>
+        <v>0.7411677753141168</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6930379746835442</v>
+        <v>0.7036837376460018</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7228617536309844</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6619812583668006</v>
+        <v>0.6957831325301205</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7076998964384436</v>
+        <v>0.7196824708963694</v>
       </c>
     </row>
     <row r="11">
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8651288158383005</v>
+        <v>0.8515904964874892</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8343338118230458</v>
+        <v>0.8423152805179649</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8135326212249289</v>
+        <v>0.8222789115646257</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8278261561095868</v>
+        <v>0.8450435404986282</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8352053512489654</v>
+        <v>0.840307057267177</v>
       </c>
     </row>
     <row r="12">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8977272727272727</v>
+        <v>0.9083333333333333</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8910256410256411</v>
+        <v>0.9001831501831502</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9092391304347827</v>
+        <v>0.8918478260869565</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8146067415730337</v>
+        <v>0.8342696629213483</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8781496964401825</v>
+        <v>0.8836584931311972</v>
       </c>
     </row>
     <row r="13">
@@ -721,27 +721,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[77, 11], [4, 11]]</t>
+          <t>[[74, 14], [3, 12]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[70, 14], [4, 9]]</t>
+          <t>[[71, 13], [4, 9]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[73, 19], [4, 16]]</t>
+          <t>[[73, 19], [3, 17]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[73, 16], [4, 8]]</t>
+          <t>[[74, 15], [3, 9]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[73, 15], [4, 11]]</t>
+          <t>[[73, 15], [3, 12]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8163562442230539</v>
+        <v>0.8212618327852916</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02305864927694515</v>
+        <v>0.01132188569162289</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7767930007014643</v>
+        <v>0.8004242266852183</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02477114771248951</v>
+        <v>0.02208685787230244</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7076998964384436</v>
+        <v>0.7196824708963694</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03383703148217181</v>
+        <v>0.02017291588866053</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8352053512489654</v>
+        <v>0.840307057267177</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01884365318615214</v>
+        <v>0.01094071835093245</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8781496964401825</v>
+        <v>0.8836584931311972</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03726033904031788</v>
+        <v>0.02910426838731383</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[73, 15], [4, 11]]</t>
+          <t>[[73, 15], [3, 12]]</t>
         </is>
       </c>
     </row>
